--- a/docs/specs-seed/northhs-2026-07-30/product-specs-template.xlsx
+++ b/docs/specs-seed/northhs-2026-07-30/product-specs-template.xlsx
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>ENTERTAINMENT LUMINAIRES MOVING</t>
+          <t>AUTOMATED PROFILE FIXTURE</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2914,37 +2914,32 @@
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>No heading in the source — Spec Title taken from the article.</t>
-        </is>
-      </c>
+      <c r="H41" s="4" t="inlineStr"/>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Permission to bid does not imply acceptance of the manufacturer Automated Profile Fixture
-  Basis of Design: Lonestar as manufactured by ETC Inc.
-  Standards Compliance:
-    Listed: UL 1573, and CE Certification
-  Array:
-    Ultra-Bright 7000K
-  Features:
-    Four Plane Shutter System
-    Nine Rotating Interchangeable Gobos
-    CYM Subtractive Color Mixing
-    Ten Interchangeable Colors
-      Red, blue, green, yellow, orange, purple, TM-30 filter, lavender, half CTO, full CTO, and dark blue
-    Pan Tilt and Zoom
-      Pan 540 Degrees, 360 movement in 2.3s
-      Tilt 270 Degrees, 180 movement in 1.26s
-      Zoom 3.8-55 Degrees
-  Control:
-    Input Method:
-      DMX-512 via 5-Pin. Protocols: DMX512, RDM.
-      Ethernet via RJ45, Protocols: SACN, ArtNet
-  Electrical:
-    Input Method: powerCON True1 TOP in and thru.
-    Fixtures per Circuit:
-      Two</t>
+          <t>Basis of Design: Lonestar as manufactured by ETC Inc.
+Standards Compliance:
+  Listed: UL 1573, and CE Certification
+Array:
+  Ultra-Bright 7000K
+Features:
+  Four Plane Shutter System
+  Nine Rotating Interchangeable Gobos
+  CYM Subtractive Color Mixing
+  Ten Interchangeable Colors
+    Red, blue, green, yellow, orange, purple, TM-30 filter, lavender, half CTO, full CTO, and dark blue
+  Pan Tilt and Zoom
+    Pan 540 Degrees, 360 movement in 2.3s
+    Tilt 270 Degrees, 180 movement in 1.26s
+    Zoom 3.8-55 Degrees
+Control:
+  Input Method:
+    DMX-512 via 5-Pin. Protocols: DMX512, RDM.
+    Ethernet via RJ45, Protocols: SACN, ArtNet
+Electrical:
+  Input Method: powerCON True1 TOP in and thru.
+  Fixtures per Circuit:
+    Two</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
